--- a/artfynd/A 28829-2025 artfynd.xlsx
+++ b/artfynd/A 28829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017152</v>
       </c>
       <c r="B2" t="n">
-        <v>92522</v>
+        <v>92530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28829-2025 artfynd.xlsx
+++ b/artfynd/A 28829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017152</v>
       </c>
       <c r="B2" t="n">
-        <v>92530</v>
+        <v>92534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28829-2025 artfynd.xlsx
+++ b/artfynd/A 28829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017152</v>
       </c>
       <c r="B2" t="n">
-        <v>92534</v>
+        <v>92536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28829-2025 artfynd.xlsx
+++ b/artfynd/A 28829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017152</v>
       </c>
       <c r="B2" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28829-2025 artfynd.xlsx
+++ b/artfynd/A 28829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017152</v>
       </c>
       <c r="B2" t="n">
-        <v>92538</v>
+        <v>92540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28829-2025 artfynd.xlsx
+++ b/artfynd/A 28829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017152</v>
       </c>
       <c r="B2" t="n">
-        <v>92540</v>
+        <v>92544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28829-2025 artfynd.xlsx
+++ b/artfynd/A 28829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017152</v>
       </c>
       <c r="B2" t="n">
-        <v>92544</v>
+        <v>92547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
